--- a/Outputs/Scenarios/PtX_demand_MT_Electrification.xlsx
+++ b/Outputs/Scenarios/PtX_demand_MT_Electrification.xlsx
@@ -698,7 +698,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>8.397989397361691e-07</v>
+        <v>8.397989397361689e-07</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -735,7 +735,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>3.691412585452614e-06</v>
+        <v>3.691412585452613e-06</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -809,7 +809,7 @@
         <v>0.001122108264784799</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0001757780853667029</v>
+        <v>0.0001757780853667028</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1555,7 +1555,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0.001927649333441993</v>
+        <v>0.001927649333441992</v>
       </c>
     </row>
     <row r="31">
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.001927649333441993</v>
+        <v>0.001927649333441992</v>
       </c>
     </row>
     <row r="34">

--- a/Outputs/Scenarios/PtX_demand_MT_Electrification.xlsx
+++ b/Outputs/Scenarios/PtX_demand_MT_Electrification.xlsx
@@ -1037,7 +1037,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0003274048762444672</v>
+        <v>0.0003484563351089362</v>
       </c>
     </row>
     <row r="17">
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>5.456747937407788e-05</v>
+        <v>7.229842503574039e-05</v>
       </c>
     </row>
     <row r="18">
@@ -1111,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0002182699174963115</v>
+        <v>0.0002891937001429615</v>
       </c>
     </row>
     <row r="19">
@@ -1148,7 +1148,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0003274048762444672</v>
+        <v>0.0002891937001429615</v>
       </c>
     </row>
     <row r="20">
@@ -1333,7 +1333,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0004531833072539196</v>
+        <v>0.0004449160870333102</v>
       </c>
     </row>
     <row r="25">
@@ -1370,7 +1370,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>0.004437906210880133</v>
+        <v>0.004356947474367804</v>
       </c>
     </row>
     <row r="26">
@@ -1481,7 +1481,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>5.456747937407788e-05</v>
+        <v>7.229842503574039e-05</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0.001927649333441992</v>
+        <v>0.001880743452929848</v>
       </c>
     </row>
     <row r="31">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0.0003212748889069988</v>
+        <v>0.0003902204547396131</v>
       </c>
     </row>
     <row r="32">
@@ -1629,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.001285099555627995</v>
+        <v>0.001560881818958453</v>
       </c>
     </row>
     <row r="33">
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.001927649333441992</v>
+        <v>0.001560881818958453</v>
       </c>
     </row>
     <row r="34">
@@ -1999,7 +1999,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>0.0003212748889069988</v>
+        <v>0.0003902204547396131</v>
       </c>
     </row>
     <row r="43">
